--- a/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1,23</t>
+          <t>-6,04; 2,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,64</t>
+          <t>-3,99; 7,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,12</t>
+          <t>-7,07; 1,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,04</t>
+          <t>-3,96; 5,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 4,79</t>
+          <t>-4,31; 4,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 0,0</t>
+          <t>-8,19; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,56</t>
+          <t>-3,7; 2,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,34</t>
+          <t>-2,9; 4,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,0</t>
+          <t>-5,8; -0,09</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 247,36</t>
+          <t>-86,28; 326,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,77; 414,5</t>
+          <t>-72,03; 321,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,67</t>
+          <t>-5,6; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,94</t>
+          <t>-6,01; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,34</t>
+          <t>-5,63; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,85</t>
+          <t>-2,9; 6,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,05</t>
+          <t>-4,97; 2,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -1,2</t>
+          <t>-6,61; -1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,14</t>
+          <t>-3,02; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,28</t>
+          <t>-4,35; 1,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,18</t>
+          <t>-4,97; 0,15</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,42; 152,97</t>
+          <t>-89,27; 217,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-89,79; 140,55</t>
+          <t>-87,59; 146,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 216,64</t>
+          <t>-86,26; 163,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 433,94</t>
+          <t>-71,94; 637,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,96</t>
+          <t>-100,0; 226,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,24 +1029,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 169,3</t>
+          <t>-61,83; 179,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,86; 70,44</t>
+          <t>-79,34; 69,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,31; 25,7</t>
+          <t>-88,96; 34,13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,4</t>
+          <t>-1,01; 7,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,77</t>
+          <t>-1,82; 6,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,0</t>
+          <t>-6,2; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,76</t>
+          <t>-2,46; 5,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,3</t>
+          <t>-3,49; 2,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 15,78</t>
+          <t>1,31; 15,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,88</t>
+          <t>-0,92; 5,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,01</t>
+          <t>-1,88; 3,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 7,5</t>
+          <t>0,01; 7,89</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,74; —</t>
+          <t>-9,73; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; —</t>
+          <t>-70,53; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-40,08; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,08</t>
+          <t>-5,49; 4,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,05</t>
+          <t>-4,0; 6,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -1,18</t>
+          <t>-9,24; -1,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,85</t>
+          <t>-6,39; 2,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,03</t>
+          <t>-2,08; 9,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; -1,03</t>
+          <t>-8,44; -1,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,41</t>
+          <t>-4,05; 2,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,24</t>
+          <t>-1,41; 6,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -1,66</t>
+          <t>-7,14; -1,6</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 411,21</t>
+          <t>-100,0; 507,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,06; 470,13</t>
+          <t>-72,61; 626,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 307,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 626,18</t>
+          <t>-53,96; 700,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 139,49</t>
+          <t>-76,34; 156,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 360,48</t>
+          <t>-32,9; 341,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 8,14</t>
+          <t>-10,74; 9,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 1,79</t>
+          <t>-14,56; 1,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -4,66</t>
+          <t>-19,35; -3,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 1,37</t>
+          <t>-10,95; 1,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 4,32</t>
+          <t>-9,17; 4,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -1,49</t>
+          <t>-12,65; -1,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 3,35</t>
+          <t>-7,95; 3,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 1,52</t>
+          <t>-9,44; 1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -3,2</t>
+          <t>-12,73; -3,22</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 202,64</t>
+          <t>-79,77; 300,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 117,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-86,17; 101,92</t>
+          <t>-82,39; 92,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-89,16; 68,8</t>
+          <t>-88,76; 47,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -1,12</t>
+          <t>-9,77; -1,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,94</t>
+          <t>-6,17; 6,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,94</t>
+          <t>-6,1; 5,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,81</t>
+          <t>-5,14; 4,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -0,95</t>
+          <t>-8,33; -0,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 7,56</t>
+          <t>-3,31; 8,02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,72</t>
+          <t>-5,48; 0,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,14</t>
+          <t>-5,17; 1,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,77</t>
+          <t>-3,19; 5,18</t>
         </is>
       </c>
     </row>
@@ -1888,29 +1888,29 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,79; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 149,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 125,0</t>
+          <t>-100,0; 211,6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 350,08</t>
+          <t>-64,46; 426,92</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,32</t>
+          <t>-3,87; 0,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,36</t>
+          <t>-3,83; 1,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 8,4</t>
+          <t>0,39; 8,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,86</t>
+          <t>-2,41; 0,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,95</t>
+          <t>-1,43; 2,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,39; 16,12</t>
+          <t>4,37; 16,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,67</t>
+          <t>-2,08; 0,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,38</t>
+          <t>-1,77; 1,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,0; 12,42</t>
+          <t>3,92; 11,68</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 1654,4</t>
+          <t>-12,84; 1380,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>140,26; —</t>
+          <t>98,41; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 251,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 360,31</t>
+          <t>-82,31; 337,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>142,07; 1986,47</t>
+          <t>145,18; 1648,14</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,07</t>
+          <t>-4,1; -0,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,56</t>
+          <t>-3,23; 0,63</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,67</t>
+          <t>-3,91; 0,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,73</t>
+          <t>-2,35; 4,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,06</t>
+          <t>-2,63; 3,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,51</t>
+          <t>-3,81; 1,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,4</t>
+          <t>-2,44; 1,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,25</t>
+          <t>-2,41; 1,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,58</t>
+          <t>-3,14; 0,44</t>
         </is>
       </c>
     </row>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 222,22</t>
+          <t>-53,33; 251,52</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 220,8</t>
+          <t>-61,55; 219,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-88,43; 115,53</t>
+          <t>-87,28; 196,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 91,15</t>
+          <t>-66,18; 91,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 87,3</t>
+          <t>-69,3; 84,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,22; 47,17</t>
+          <t>-84,38; 49,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,22</t>
+          <t>-2,44; 0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,61</t>
+          <t>-2,23; 0,7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,65</t>
+          <t>-2,14; 0,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,36</t>
+          <t>-1,23; 1,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,29</t>
+          <t>-1,51; 1,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,85</t>
+          <t>-0,7; 2,68</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,53</t>
+          <t>-1,5; 0,42</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,59</t>
+          <t>-1,44; 0,48</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,32</t>
+          <t>-1,02; 1,23</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 12,02</t>
+          <t>-63,4; 12,87</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 29,17</t>
+          <t>-58,09; 36,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 33,31</t>
+          <t>-59,0; 30,14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 67,42</t>
+          <t>-37,85; 68,7</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 64,61</t>
+          <t>-43,53; 59,2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 135,14</t>
+          <t>-25,29; 127,23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 20,53</t>
+          <t>-43,62; 18,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 26,0</t>
+          <t>-42,82; 19,93</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 56,22</t>
+          <t>-32,11; 49,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,14</t>
+          <t>-6,15; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,45</t>
+          <t>-3,68; 7,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 1,28</t>
+          <t>-6,17; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,05</t>
+          <t>-3,79; 4,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,47</t>
+          <t>-4,54; 4,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 0,0</t>
+          <t>-9,5; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,65</t>
+          <t>-3,63; 2,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,2</t>
+          <t>-2,89; 4,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,09</t>
+          <t>-5,21; -0,17</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 326,64</t>
+          <t>-84,84; 292,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 321,66</t>
+          <t>-72,99; 442,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,78</t>
+          <t>-5,86; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 2,04</t>
+          <t>-5,91; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,91</t>
+          <t>-5,99; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,91</t>
+          <t>-2,83; 6,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,09</t>
+          <t>-5,17; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,2</t>
+          <t>-7,34; -1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,47</t>
+          <t>-2,9; 3,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,18</t>
+          <t>-4,37; 1,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,15</t>
+          <t>-4,88; -0,08</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 217,83</t>
+          <t>-89,96; 178,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 146,04</t>
+          <t>-88,05; 156,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 163,97</t>
+          <t>-90,47; 181,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 637,09</t>
+          <t>-69,32; 457,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,54</t>
+          <t>-100,0; 278,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 179,53</t>
+          <t>-58,76; 150,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,34; 69,48</t>
+          <t>-80,79; 65,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-88,96; 34,13</t>
+          <t>-92,53; 7,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 7,21</t>
+          <t>-1,03; 7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,7</t>
+          <t>-1,87; 5,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,0</t>
+          <t>-5,16; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,73</t>
+          <t>-2,5; 5,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,3</t>
+          <t>-3,5; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 15,02</t>
+          <t>1,27; 14,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,02</t>
+          <t>-0,85; 4,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,3</t>
+          <t>-1,85; 3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,89</t>
+          <t>0,1; 8,47</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,73; —</t>
+          <t>-46,07; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,53; —</t>
+          <t>-64,58; 1195,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,08; —</t>
+          <t>-43,33; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,84</t>
+          <t>-5,41; 4,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,65</t>
+          <t>-4,05; 6,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,1</t>
+          <t>-9,19; -1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,81</t>
+          <t>-5,38; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 9,28</t>
+          <t>-1,77; 10,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,04</t>
+          <t>-8,5; -0,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,56</t>
+          <t>-4,02; 2,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,69</t>
+          <t>-2,08; 6,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,6</t>
+          <t>-6,53; -1,59</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 507,83</t>
+          <t>-85,0; 576,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 626,22</t>
+          <t>-74,01; 545,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 700,0</t>
+          <t>-46,36; 866,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 156,93</t>
+          <t>-72,82; 168,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 341,25</t>
+          <t>-44,37; 295,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 9,28</t>
+          <t>-11,51; 8,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 1,55</t>
+          <t>-15,15; 1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -3,44</t>
+          <t>-19,22; -3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 1,41</t>
+          <t>-10,77; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 4,32</t>
+          <t>-9,18; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -1,5</t>
+          <t>-13,61; -1,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 3,43</t>
+          <t>-8,48; 2,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 1,06</t>
+          <t>-9,73; 0,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -3,22</t>
+          <t>-12,57; -3,26</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-79,77; 300,55</t>
+          <t>-83,38; 242,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 116,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 92,99</t>
+          <t>-84,94; 100,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-88,76; 47,73</t>
+          <t>-92,78; 56,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -1,11</t>
+          <t>-9,68; -1,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,09</t>
+          <t>-6,55; 5,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 5,86</t>
+          <t>-5,98; 5,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,11</t>
+          <t>-5,81; 3,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -0,96</t>
+          <t>-8,31; -0,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,02</t>
+          <t>-3,15; 8,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,71</t>
+          <t>-5,6; 0,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,45</t>
+          <t>-5,28; 1,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,18</t>
+          <t>-3,34; 4,85</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,79; —</t>
+          <t>-83,26; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,33</t>
+          <t>-100,0; 124,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,6</t>
+          <t>-100,0; 199,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 426,92</t>
+          <t>-66,97; 343,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,96</t>
+          <t>-3,43; 1,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,34</t>
+          <t>-3,48; 1,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 8,51</t>
+          <t>0,84; 9,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,86</t>
+          <t>-2,39; 0,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,85</t>
+          <t>-1,48; 2,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,37; 16,4</t>
+          <t>4,47; 16,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,65</t>
+          <t>-2,14; 0,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,5</t>
+          <t>-1,8; 1,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,68</t>
+          <t>3,78; 12,13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 1380,6</t>
+          <t>-22,97; 1532,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>98,41; —</t>
+          <t>114,07; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 210,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-82,31; 337,62</t>
+          <t>-86,65; 255,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>145,18; 1648,14</t>
+          <t>127,54; 1751,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,17</t>
+          <t>-4,25; -0,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,63</t>
+          <t>-3,56; 0,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,29</t>
+          <t>-3,77; 0,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,04</t>
+          <t>-2,6; 3,77</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,15</t>
+          <t>-3,12; 3,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,64</t>
+          <t>-4,04; 1,48</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,3</t>
+          <t>-2,47; 1,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,22</t>
+          <t>-2,43; 1,21</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,44</t>
+          <t>-3,11; 0,41</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 280,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 251,52</t>
+          <t>-58,34; 228,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-61,55; 219,63</t>
+          <t>-69,43; 183,92</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 196,47</t>
+          <t>-87,28; 111,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 91,6</t>
+          <t>-67,95; 76,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 84,83</t>
+          <t>-66,62; 82,55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 49,19</t>
+          <t>-86,96; 38,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,23</t>
+          <t>-2,57; 0,19</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,7</t>
+          <t>-2,17; 0,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,59</t>
+          <t>-2,24; 0,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,38</t>
+          <t>-1,28; 1,37</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,4; 1,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,68</t>
+          <t>-0,54; 2,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,42</t>
+          <t>-1,51; 0,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,48</t>
+          <t>-1,33; 0,56</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,23</t>
+          <t>-0,97; 1,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 12,87</t>
+          <t>-67,68; 12,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 36,04</t>
+          <t>-56,88; 24,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 30,14</t>
+          <t>-60,09; 20,88</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 68,7</t>
+          <t>-39,36; 68,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 59,2</t>
+          <t>-43,08; 65,68</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 127,23</t>
+          <t>-18,25; 140,99</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 18,5</t>
+          <t>-44,83; 20,45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 19,93</t>
+          <t>-39,6; 24,37</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 49,66</t>
+          <t>-29,83; 55,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-1,78</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 1,27</t>
+          <t>-3,85; 5,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 7,05</t>
+          <t>-4,14; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,67</t>
+          <t>-8,22; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 4,93</t>
+          <t>-6,24; 1,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 4,7</t>
+          <t>-4,31; 6,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,0</t>
+          <t>-6,16; 2,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,45</t>
+          <t>-3,51; 2,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,24</t>
+          <t>-2,49; 4,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; -0,17</t>
+          <t>-5,08; 0,1</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-64,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>27,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-65,02%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-58,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-80,94%</t>
+          <t>-78,19%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 292,63</t>
+          <t>-85,98; 247,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 442,34</t>
+          <t>-66,77; 414,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,59</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-1,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 3,0</t>
+          <t>-2,94; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 2,13</t>
+          <t>-5,09; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,94</t>
+          <t>-7,09; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,14</t>
+          <t>-5,4; 2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,02</t>
+          <t>-6,17; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; -1,2</t>
+          <t>-4,8; 4,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,51</t>
+          <t>-3,07; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,14</t>
+          <t>-4,01; 1,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,08</t>
+          <t>-4,42; 0,77</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-38,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-31,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-38,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-27,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-38,93%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-6,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-59,04%</t>
+          <t>-50,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,96; 178,71</t>
+          <t>-68,04; 433,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 156,23</t>
+          <t>-100,0; 148,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,47; 181,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 457,38</t>
+          <t>-87,42; 152,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 278,01</t>
+          <t>-89,79; 140,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,84; 270,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 150,95</t>
+          <t>-60,72; 169,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,79; 65,52</t>
+          <t>-79,86; 70,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,53; 7,27</t>
+          <t>-87,14; 58,74</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,21</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-1,02</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,89</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,6</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 7,28</t>
+          <t>-2,48; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,94</t>
+          <t>-3,5; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,0</t>
+          <t>0,9; 14,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,72</t>
+          <t>-1,05; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,28</t>
+          <t>-1,88; 5,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,5</t>
+          <t>-4,92; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,99</t>
+          <t>-0,87; 4,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,01</t>
+          <t>-1,89; 3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,47</t>
+          <t>-0,18; 6,41</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63,55%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>356,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>207,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>122,35%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63,55%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-39,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>395,95%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>115,36%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>232,92%</t>
+          <t>193,25%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,41; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,07; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,58; 1195,89</t>
+          <t>-71,8; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-3,66</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,22</t>
+          <t>-5,69; 2,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 6,24</t>
+          <t>-1,79; 9,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -1,05</t>
+          <t>-8,4; -1,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 3,6</t>
+          <t>-5,63; 4,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 10,09</t>
+          <t>-4,09; 6,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; -0,76</t>
+          <t>-9,49; -1,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,53</t>
+          <t>-4,1; 2,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,02</t>
+          <t>-1,47; 6,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,53; -1,59</t>
+          <t>-7,07; -1,66</t>
         </is>
       </c>
     </row>
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-27,09%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>94,54%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-10,22%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>33,06%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-27,09%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 576,07</t>
+          <t>-100,0; 307,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 545,7</t>
+          <t>-47,7; 626,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,81; 411,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 866,51</t>
+          <t>-76,06; 470,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 168,66</t>
+          <t>-76,21; 139,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 295,22</t>
+          <t>-31,0; 360,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,22</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,67</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-6,37</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-9,71</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,22</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 8,29</t>
+          <t>-9,57; 1,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 1,49</t>
+          <t>-9,06; 4,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,22; -3,23</t>
+          <t>-12,18; -1,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 1,37</t>
+          <t>-12,54; 8,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 4,7</t>
+          <t>-15,63; 1,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -1,49</t>
+          <t>-18,34; -4,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 2,66</t>
+          <t>-8,74; 3,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 0,92</t>
+          <t>-9,29; 1,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -3,26</t>
+          <t>-12,03; -3,2</t>
         </is>
       </c>
     </row>
@@ -1594,27 +1594,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-68,91%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-35,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,63%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-65,63%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-68,91%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-35,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 242,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,26; 202,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 117,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-84,94; 100,11</t>
+          <t>-86,17; 101,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-92,78; 56,38</t>
+          <t>-89,16; 68,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,71</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,08</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-3,63</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,54</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,08</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -1,11</t>
+          <t>-5,16; 3,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 5,62</t>
+          <t>-8,14; -0,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 5,17</t>
+          <t>-3,21; 8,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 3,88</t>
+          <t>-9,67; -1,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -0,96</t>
+          <t>-6,13; 5,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 8,18</t>
+          <t>-6,3; 4,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,79</t>
+          <t>-5,67; 0,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 1,35</t>
+          <t>-5,29; 1,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,85</t>
+          <t>-3,1; 4,99</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-23,12%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>70,13%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-14,8%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-18,57%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-23,12%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>-19,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,26; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,25</t>
+          <t>-100,0; 125,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 343,74</t>
+          <t>-65,62; 364,01</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8,37</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4,31</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,01</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,66</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,35</t>
+          <t>-2,85; 0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,32</t>
+          <t>-1,43; 2,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,42</t>
+          <t>3,73; 13,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,89</t>
+          <t>-3,43; 1,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,85</t>
+          <t>-3,26; 1,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,47; 16,4</t>
+          <t>0,77; 9,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,46</t>
+          <t>-2,13; 0,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,29</t>
+          <t>-1,6; 1,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,13</t>
+          <t>3,8; 10,98</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-53,41%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>51,4%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>877,76%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-41,3%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-42,19%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>260,06%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-53,41%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>51,4%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>944,57%</t>
+          <t>285,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>531,9%</t>
+          <t>514,31%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 1532,49</t>
+          <t>163,6; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>114,07; —</t>
+          <t>-2,97; 1733,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,26</t>
+          <t>-100,0; 251,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 255,8</t>
+          <t>-79,0; 360,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127,54; 1751,5</t>
+          <t>132,08; 1792,8</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,22</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,23</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -0,13</t>
+          <t>-2,6; 3,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,41</t>
+          <t>-2,86; 3,06</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,59</t>
+          <t>-4,02; 1,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,77</t>
+          <t>-4,22; -0,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,01</t>
+          <t>-3,86; 0,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,48</t>
+          <t>-3,44; 0,86</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,19</t>
+          <t>-2,25; 1,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,21</t>
+          <t>-2,54; 1,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,41</t>
+          <t>-2,9; 0,66</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-37,4%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-81,39%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-61,63%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-71,18%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>18,88%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-38,42%</t>
+          <t>-68,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-49,1%</t>
+          <t>-48,2%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,51</t>
+          <t>-64,74; 222,22</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,35; 220,8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,28; 123,12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 228,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 183,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 111,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-67,95; 76,19</t>
+          <t>-64,64; 91,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 82,55</t>
+          <t>-72,32; 87,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-86,96; 38,96</t>
+          <t>-83,54; 55,4</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,19</t>
+          <t>-1,37; 1,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,51</t>
+          <t>-1,42; 1,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,45</t>
+          <t>-0,81; 2,26</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,37</t>
+          <t>-2,49; 0,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,27</t>
+          <t>-2,14; 0,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,94</t>
+          <t>-2,23; 0,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,51; 0,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,56</t>
+          <t>-1,46; 0,59</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,28</t>
+          <t>-1,01; 1,17</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-3,09%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-36,91%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-25,79%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-29,74%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>-23,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 12,23</t>
+          <t>-40,66; 67,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 24,42</t>
+          <t>-44,02; 64,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 20,88</t>
+          <t>-25,31; 110,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 68,5</t>
+          <t>-66,07; 12,02</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 65,68</t>
+          <t>-58,05; 29,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 140,99</t>
+          <t>-58,9; 43,52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 20,45</t>
+          <t>-44,99; 20,53</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 24,37</t>
+          <t>-43,15; 26,0</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 55,89</t>
+          <t>-32,25; 52,22</t>
         </is>
       </c>
     </row>
